--- a/data/trans_bre/P16A13-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A13-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,81</t>
+          <t>-0,95; 2,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,54</t>
+          <t>-0,83; 3,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,35</t>
+          <t>0,26; 4,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,82</t>
+          <t>2,02; 8,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 76,61</t>
+          <t>-17,93; 75,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 63,71</t>
+          <t>-10,35; 62,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 142,72</t>
+          <t>4,3; 128,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,55; 79,98</t>
+          <t>12,74; 77,04</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,23</t>
+          <t>0,32; 2,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,59</t>
+          <t>-0,89; 1,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,28</t>
+          <t>-0,69; 1,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,58</t>
+          <t>-1,12; 2,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 219,0</t>
+          <t>10,78; 224,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 68,9</t>
+          <t>-26,71; 70,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 72,04</t>
+          <t>-24,86; 71,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 73,04</t>
+          <t>-20,52; 67,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,34</t>
+          <t>-3,24; 0,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,55</t>
+          <t>-1,44; 4,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,82</t>
+          <t>-1,64; 2,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,04</t>
+          <t>-3,19; 0,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,95; 34,33</t>
+          <t>-81,22; 36,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 209,16</t>
+          <t>-32,79; 206,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,65; 175,75</t>
+          <t>-43,91; 192,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 23,9</t>
+          <t>-46,24; 22,15</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,77</t>
+          <t>0,08; 1,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,23</t>
+          <t>0,25; 2,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,04</t>
+          <t>0,29; 2,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,43</t>
+          <t>0,19; 3,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 78,22</t>
+          <t>1,76; 85,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 63,54</t>
+          <t>4,88; 65,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 82,08</t>
+          <t>9,21; 88,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 70,03</t>
+          <t>3,65; 62,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A13-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A13-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,76</t>
+          <t>-0,81; 2,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,43</t>
+          <t>-0,86; 3,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,75</t>
+          <t>0,5; 5,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,49</t>
+          <t>2,69; 8,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 75,7</t>
+          <t>-14,72; 77,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 62,53</t>
+          <t>-11,05; 63,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 128,37</t>
+          <t>6,84; 142,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,74; 77,04</t>
+          <t>17,89; 84,22</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,27</t>
+          <t>0,25; 2,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,67</t>
+          <t>-0,98; 1,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,33</t>
+          <t>-0,78; 1,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,43</t>
+          <t>-0,1; 2,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,78; 224,11</t>
+          <t>11,21; 230,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 70,3</t>
+          <t>-28,49; 69,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 71,01</t>
+          <t>-25,47; 71,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 67,57</t>
+          <t>-1,21; 58,53</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-18,94%</t>
+          <t>-18,2%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,28</t>
+          <t>-3,37; 0,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,6</t>
+          <t>-1,56; 4,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,82</t>
+          <t>-1,73; 2,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,99</t>
+          <t>-3,18; 1,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,22; 36,68</t>
+          <t>-83,88; 31,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 206,42</t>
+          <t>-31,02; 210,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 192,89</t>
+          <t>-46,0; 169,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 22,15</t>
+          <t>-43,89; 22,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,82</t>
+          <t>0,08; 1,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,33</t>
+          <t>0,28; 2,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,16</t>
+          <t>0,27; 2,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,25</t>
+          <t>1,01; 3,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 85,31</t>
+          <t>1,07; 74,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 65,18</t>
+          <t>5,74; 66,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 88,26</t>
+          <t>8,02; 87,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 62,49</t>
+          <t>14,93; 55,98</t>
         </is>
       </c>
     </row>
